--- a/WordSearchTools/word_search/Assets/Excel/Primary关卡数据.xlsx
+++ b/WordSearchTools/word_search/Assets/Excel/Primary关卡数据.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
   <si>
     <t>#Primary</t>
   </si>
@@ -96,6 +96,27 @@
   </si>
   <si>
     <t>such</t>
+  </si>
+  <si>
+    <t>BEAR</t>
+  </si>
+  <si>
+    <t>BED</t>
+  </si>
+  <si>
+    <t>COW</t>
+  </si>
+  <si>
+    <t>JAGUAR</t>
+  </si>
+  <si>
+    <t>LION</t>
+  </si>
+  <si>
+    <t>MOUSE</t>
+  </si>
+  <si>
+    <t>STOOL</t>
   </si>
   <si>
     <t>food</t>
@@ -1349,8 +1370,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.7692307692308" customWidth="1"/>
     <col min="2" max="2" width="15.3846153846154" customWidth="1"/>
@@ -1358,7 +1379,7 @@
     <col min="6" max="6" width="8.76923076923077" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:7">
+    <row r="1" customFormat="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1375,7 +1396,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="17" spans="1:7">
+    <row r="2" s="1" customFormat="1" ht="17" spans="1:8">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1394,7 +1415,7 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" customFormat="1" spans="1:7">
+    <row r="3" customFormat="1" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1409,7 +1430,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" customFormat="1" spans="1:7">
+    <row r="4" customFormat="1" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1422,7 +1443,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" customFormat="1" spans="1:7">
+    <row r="5" customFormat="1" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1439,7 +1460,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" s="1" customFormat="1" ht="17" spans="1:7">
+    <row r="6" s="1" customFormat="1" ht="17" spans="1:8">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -1460,7 +1481,7 @@
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" customFormat="1" spans="1:7">
+    <row r="7" customFormat="1" spans="1:8">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1473,7 +1494,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" customFormat="1" spans="1:7">
+    <row r="8" customFormat="1" spans="1:8">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -1486,7 +1507,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
@@ -1503,7 +1524,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" s="1" customFormat="1" ht="17" spans="1:7">
+    <row r="10" s="1" customFormat="1" ht="17" spans="1:8">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
@@ -1524,7 +1545,7 @@
       </c>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -1539,7 +1560,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1550,152 +1571,151 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="6" t="s">
+    <row r="13" customFormat="1" spans="1:8">
+      <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>4</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="17" spans="1:8">
+      <c r="A14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:8">
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:8">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="7">
         <v>1</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" ht="17" spans="1:7">
-      <c r="A14" s="8" t="s">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" ht="17" spans="1:7">
+      <c r="A18" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="B18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="E18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="6" t="s">
+    <row r="19" spans="1:7">
+      <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="6" t="s">
+      <c r="B19" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" customFormat="1" spans="1:7">
-      <c r="A17" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="10">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-    </row>
-    <row r="18" ht="17" spans="1:7">
-      <c r="A18" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="10" t="s">
+      <c r="B20" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G18" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" spans="1:7">
-      <c r="A19" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-    </row>
-    <row r="20" customFormat="1" spans="1:7">
-      <c r="A20" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21" customFormat="1" spans="1:7">
       <c r="A21" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D21" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -1706,26 +1726,30 @@
         <v>3</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+        <v>43</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="23" customFormat="1" spans="1:7">
       <c r="A23" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -1738,7 +1762,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -1746,6 +1770,68 @@
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
     </row>
+    <row r="25" customFormat="1" spans="1:7">
+      <c r="A25" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="10">
+        <v>2</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" ht="17" spans="1:7">
+      <c r="A26" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27" customFormat="1" spans="1:7">
+      <c r="A27" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:7">
+      <c r="A28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
